--- a/outputs/141-20.xlsx
+++ b/outputs/141-20.xlsx
@@ -149,20 +149,24 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -358,22 +362,22 @@
   <dimension ref="A1:D1"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="15.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="34.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="13.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="15.72"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
     </row>
@@ -396,58 +400,58 @@
   <dimension ref="A1:I2"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="10.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="10.71"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="I1" s="1" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="0" t="n">
+      <c r="D2" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="E2" s="0" t="n">
+      <c r="E2" s="1" t="n">
         <v>2023</v>
       </c>
-      <c r="F2" s="0" t="n">
+      <c r="F2" s="1" t="n">
         <v>9963585</v>
       </c>
-      <c r="H2" s="3" t="n">
+      <c r="H2" s="4" t="n">
         <v>44917</v>
       </c>
-      <c r="I2" s="0" t="n">
+      <c r="I2" s="1" t="n">
         <v>885.65</v>
       </c>
     </row>
